--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1140,7 +1140,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260716085852</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1226,7 +1226,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260716085851</t>
   </si>
   <si>
     <t>OBX-17</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-observation-microorganism-detection-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
